--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T18:59:27+03:00</t>
+    <t>2026-03-22T11:14:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T11:14:06+05:30</t>
+    <t>2026-03-22T13:21:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6973" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7105" uniqueCount="722">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T13:21:26+05:30</t>
+    <t>2026-03-25T09:53:08+03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1228,6 +1228,9 @@
 middle name</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Given names (not always 'first'). Includes middle names</t>
   </si>
   <si>
@@ -1674,9 +1677,6 @@
     <t>Patient.contact.relationship.coding</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
@@ -1937,9 +1937,6 @@
   </si>
   <si>
     <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Practitioner/456789</t>
   </si>
   <si>
     <t>Reference.reference</t>
@@ -2194,6 +2191,65 @@
   </si>
   <si>
     <t>Extension.extension:period.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].start</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Period.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per-1
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:period.value[x].end</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x].end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
+    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
+  </si>
+  <si>
+    <t>If the end of the period is missing, it means that the period is ongoing</t>
+  </si>
+  <si>
+    <t>Period.end</t>
   </si>
   <si>
     <t>base64Binary
@@ -2679,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="45">
@@ -2687,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="46">
@@ -2703,7 +2759,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="48">
@@ -2797,7 +2853,7 @@
         <v>27</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="60">
@@ -2813,7 +2869,7 @@
         <v>31</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="62">
@@ -2834,10 +2890,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -2847,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK206"/>
+  <dimension ref="A1:AK210"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.30859375" customWidth="true" bestFit="true"/>
@@ -10503,7 +10559,7 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>75</v>
@@ -10521,13 +10577,13 @@
         <v>215</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -10577,7 +10633,7 @@
         <v>76</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>74</v>
@@ -10597,10 +10653,10 @@
         <v>304</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10626,10 +10682,10 @@
         <v>215</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
@@ -10680,7 +10736,7 @@
         <v>76</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>74</v>
@@ -10700,10 +10756,10 @@
         <v>304</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10729,10 +10785,10 @@
         <v>215</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -10783,7 +10839,7 @@
         <v>76</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>74</v>
@@ -10803,10 +10859,10 @@
         <v>304</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10832,14 +10888,14 @@
         <v>255</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>76</v>
@@ -10888,7 +10944,7 @@
         <v>76</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>74</v>
@@ -10983,10 +11039,10 @@
         <v>76</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AD77" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AE77" t="s" s="2">
         <v>76</v>
@@ -11015,10 +11071,10 @@
         <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11118,10 +11174,10 @@
         <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11223,10 +11279,10 @@
         <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11252,10 +11308,10 @@
         <v>102</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
@@ -11285,10 +11341,10 @@
         <v>166</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA80" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AB80" t="s" s="2">
         <v>76</v>
@@ -11306,7 +11362,7 @@
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>74</v>
@@ -11315,7 +11371,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>94</v>
@@ -11326,10 +11382,10 @@
         <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11355,16 +11411,16 @@
         <v>215</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P81" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>76</v>
@@ -11413,7 +11469,7 @@
         <v>76</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>74</v>
@@ -11433,10 +11489,10 @@
         <v>304</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11462,16 +11518,16 @@
         <v>102</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P82" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>76</v>
@@ -11499,10 +11555,10 @@
         <v>166</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AB82" t="s" s="2">
         <v>76</v>
@@ -11520,7 +11576,7 @@
         <v>76</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>74</v>
@@ -11540,10 +11596,10 @@
         <v>304</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11566,16 +11622,16 @@
         <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
@@ -11625,7 +11681,7 @@
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>74</v>
@@ -11645,10 +11701,10 @@
         <v>304</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11674,10 +11730,10 @@
         <v>255</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -11728,7 +11784,7 @@
         <v>76</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>74</v>
@@ -11748,13 +11804,13 @@
         <v>304</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>155</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E85" t="s" s="2">
         <v>76</v>
@@ -11779,7 +11835,7 @@
         <v>156</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>158</v>
@@ -11857,10 +11913,10 @@
         <v>304</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11960,10 +12016,10 @@
         <v>304</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -12065,10 +12121,10 @@
         <v>304</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12094,10 +12150,10 @@
         <v>102</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
@@ -12109,7 +12165,7 @@
         <v>76</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>76</v>
@@ -12127,10 +12183,10 @@
         <v>166</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AB88" t="s" s="2">
         <v>76</v>
@@ -12148,7 +12204,7 @@
         <v>76</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>74</v>
@@ -12157,7 +12213,7 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>94</v>
@@ -12168,10 +12224,10 @@
         <v>304</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12197,16 +12253,16 @@
         <v>215</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P89" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>76</v>
@@ -12255,7 +12311,7 @@
         <v>76</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>74</v>
@@ -12275,10 +12331,10 @@
         <v>304</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -12304,16 +12360,16 @@
         <v>102</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P90" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q90" t="s" s="2">
         <v>76</v>
@@ -12323,7 +12379,7 @@
         <v>76</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>76</v>
@@ -12341,10 +12397,10 @@
         <v>166</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AB90" t="s" s="2">
         <v>76</v>
@@ -12362,7 +12418,7 @@
         <v>76</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>74</v>
@@ -12382,10 +12438,10 @@
         <v>304</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12408,16 +12464,16 @@
         <v>83</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
@@ -12467,7 +12523,7 @@
         <v>76</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>74</v>
@@ -12487,10 +12543,10 @@
         <v>304</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12516,10 +12572,10 @@
         <v>255</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -12570,7 +12626,7 @@
         <v>76</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>74</v>
@@ -13018,10 +13074,10 @@
         <v>304</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13121,10 +13177,10 @@
         <v>304</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13226,10 +13282,10 @@
         <v>304</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13255,16 +13311,16 @@
         <v>102</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P99" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q99" t="s" s="2">
         <v>76</v>
@@ -13274,10 +13330,10 @@
         <v>76</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="U99" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="V99" t="s" s="2">
         <v>76</v>
@@ -13292,10 +13348,10 @@
         <v>166</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA99" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>76</v>
@@ -13313,7 +13369,7 @@
         <v>76</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>74</v>
@@ -13333,10 +13389,10 @@
         <v>304</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13362,13 +13418,13 @@
         <v>102</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
@@ -13382,7 +13438,7 @@
         <v>76</v>
       </c>
       <c r="U100" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="V100" t="s" s="2">
         <v>76</v>
@@ -13397,10 +13453,10 @@
         <v>166</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA100" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>76</v>
@@ -13418,7 +13474,7 @@
         <v>76</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>74</v>
@@ -13438,10 +13494,10 @@
         <v>304</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13467,13 +13523,13 @@
         <v>215</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>377</v>
@@ -13489,7 +13545,7 @@
         <v>76</v>
       </c>
       <c r="U101" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="V101" t="s" s="2">
         <v>76</v>
@@ -13525,7 +13581,7 @@
         <v>76</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>74</v>
@@ -13545,10 +13601,10 @@
         <v>304</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13559,7 +13615,7 @@
         <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>76</v>
@@ -13574,10 +13630,10 @@
         <v>215</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -13592,7 +13648,7 @@
         <v>76</v>
       </c>
       <c r="U102" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="V102" t="s" s="2">
         <v>76</v>
@@ -13628,7 +13684,7 @@
         <v>76</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>74</v>
@@ -13648,10 +13704,10 @@
         <v>304</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13677,10 +13733,10 @@
         <v>215</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
@@ -13751,10 +13807,10 @@
         <v>304</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13852,13 +13908,13 @@
         <v>304</v>
       </c>
       <c r="B105" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="C105" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="D105" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E105" t="s" s="2">
         <v>76</v>
@@ -13880,13 +13936,13 @@
         <v>76</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M105" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="N105" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -13957,10 +14013,10 @@
         <v>304</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13986,10 +14042,10 @@
         <v>215</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -14013,7 +14069,7 @@
         <v>76</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Y106" t="s" s="2">
         <v>76</v>
@@ -14040,7 +14096,7 @@
         <v>76</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>74</v>
@@ -14060,14 +14116,14 @@
         <v>304</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
@@ -14089,10 +14145,10 @@
         <v>215</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -14107,7 +14163,7 @@
         <v>76</v>
       </c>
       <c r="U107" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="V107" t="s" s="2">
         <v>76</v>
@@ -14143,7 +14199,7 @@
         <v>76</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>74</v>
@@ -14163,14 +14219,14 @@
         <v>304</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" t="s" s="2">
@@ -14192,13 +14248,13 @@
         <v>215</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -14212,7 +14268,7 @@
         <v>76</v>
       </c>
       <c r="U108" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="V108" t="s" s="2">
         <v>76</v>
@@ -14248,7 +14304,7 @@
         <v>76</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>74</v>
@@ -14268,14 +14324,14 @@
         <v>304</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" t="s" s="2">
@@ -14297,10 +14353,10 @@
         <v>215</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -14351,7 +14407,7 @@
         <v>76</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>74</v>
@@ -14371,14 +14427,14 @@
         <v>304</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" t="s" s="2">
@@ -14400,10 +14456,10 @@
         <v>215</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -14418,7 +14474,7 @@
         <v>76</v>
       </c>
       <c r="U110" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="V110" t="s" s="2">
         <v>76</v>
@@ -14454,7 +14510,7 @@
         <v>76</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>74</v>
@@ -14474,10 +14530,10 @@
         <v>304</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14503,13 +14559,13 @@
         <v>215</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
@@ -14559,7 +14615,7 @@
         <v>76</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>74</v>
@@ -14579,10 +14635,10 @@
         <v>304</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14608,14 +14664,14 @@
         <v>255</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q112" t="s" s="2">
         <v>76</v>
@@ -14628,7 +14684,7 @@
         <v>76</v>
       </c>
       <c r="U112" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="V112" t="s" s="2">
         <v>76</v>
@@ -14664,7 +14720,7 @@
         <v>76</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>74</v>
@@ -15530,10 +15586,10 @@
         <v>304</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -15633,10 +15689,10 @@
         <v>304</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -15738,10 +15794,10 @@
         <v>304</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15749,10 +15805,10 @@
       </c>
       <c r="F123" s="2"/>
       <c r="G123" t="s" s="2">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>76</v>
@@ -15846,7 +15902,7 @@
         <v>541</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>542</v>
@@ -16692,7 +16748,7 @@
         <v>581</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>582</v>
@@ -18303,13 +18359,13 @@
         <v>215</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P147" s="2"/>
       <c r="Q147" t="s" s="2">
@@ -18359,7 +18415,7 @@
         <v>76</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>74</v>
@@ -18408,10 +18464,10 @@
         <v>215</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -18462,7 +18518,7 @@
         <v>76</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>74</v>
@@ -18511,10 +18567,10 @@
         <v>215</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -18565,7 +18621,7 @@
         <v>76</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>74</v>
@@ -18614,14 +18670,14 @@
         <v>255</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q150" t="s" s="2">
         <v>76</v>
@@ -18670,7 +18726,7 @@
         <v>76</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>74</v>
@@ -19862,10 +19918,10 @@
       </c>
       <c r="F162" s="2"/>
       <c r="G162" t="s" s="2">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>532</v>
+        <v>387</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>76</v>
@@ -20315,55 +20371,55 @@
         <v>76</v>
       </c>
       <c r="T166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG166" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="U166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG166" t="s" s="2">
+      <c r="AH166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>94</v>
@@ -20374,10 +20430,10 @@
         <v>304</v>
       </c>
       <c r="B167" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C167" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="C167" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -20403,13 +20459,13 @@
         <v>96</v>
       </c>
       <c r="M167" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
@@ -20438,28 +20494,28 @@
         <v>192</v>
       </c>
       <c r="Z167" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AA167" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AA167" t="s" s="2">
+      <c r="AB167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG167" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG167" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>74</v>
@@ -20479,10 +20535,10 @@
         <v>304</v>
       </c>
       <c r="B168" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C168" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="C168" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -20508,13 +20564,13 @@
         <v>138</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -20564,7 +20620,7 @@
         <v>76</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>74</v>
@@ -20584,10 +20640,10 @@
         <v>304</v>
       </c>
       <c r="B169" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C169" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -20613,13 +20669,13 @@
         <v>215</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
@@ -20669,7 +20725,7 @@
         <v>76</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>74</v>
@@ -20689,13 +20745,13 @@
         <v>304</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C170" t="s" s="2">
         <v>276</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E170" t="s" s="2">
         <v>277</v>
@@ -20796,7 +20852,7 @@
         <v>304</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>611</v>
@@ -20899,7 +20955,7 @@
         <v>304</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>613</v>
@@ -21004,7 +21060,7 @@
         <v>304</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>615</v>
@@ -21089,16 +21145,16 @@
         <v>76</v>
       </c>
       <c r="AG173" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AH173" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ173" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>94</v>
@@ -21109,10 +21165,10 @@
         <v>304</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21138,13 +21194,13 @@
         <v>96</v>
       </c>
       <c r="M174" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N174" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="P174" s="2"/>
       <c r="Q174" t="s" s="2">
@@ -21173,28 +21229,28 @@
         <v>192</v>
       </c>
       <c r="Z174" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AA174" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AA174" t="s" s="2">
+      <c r="AB174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG174" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AB174" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC174" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD174" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE174" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF174" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG174" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>74</v>
@@ -21214,10 +21270,10 @@
         <v>304</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21243,13 +21299,13 @@
         <v>138</v>
       </c>
       <c r="M175" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N175" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P175" s="2"/>
       <c r="Q175" t="s" s="2">
@@ -21299,7 +21355,7 @@
         <v>76</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>74</v>
@@ -21319,10 +21375,10 @@
         <v>304</v>
       </c>
       <c r="B176" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -21422,10 +21478,10 @@
         <v>304</v>
       </c>
       <c r="B177" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="C177" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -21527,10 +21583,10 @@
         <v>304</v>
       </c>
       <c r="B178" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C178" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -21634,10 +21690,10 @@
         <v>304</v>
       </c>
       <c r="B179" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C179" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -21741,10 +21797,10 @@
         <v>304</v>
       </c>
       <c r="B180" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -21789,7 +21845,7 @@
         <v>76</v>
       </c>
       <c r="T180" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="U180" t="s" s="2">
         <v>346</v>
@@ -21848,10 +21904,10 @@
         <v>304</v>
       </c>
       <c r="B181" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C181" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -21894,7 +21950,7 @@
         <v>76</v>
       </c>
       <c r="T181" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="U181" t="s" s="2">
         <v>352</v>
@@ -21953,10 +22009,10 @@
         <v>304</v>
       </c>
       <c r="B182" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C182" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -22056,10 +22112,10 @@
         <v>304</v>
       </c>
       <c r="B183" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C183" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="C183" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -22161,10 +22217,10 @@
         <v>304</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -22190,13 +22246,13 @@
         <v>215</v>
       </c>
       <c r="M184" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N184" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="N184" t="s" s="2">
+      <c r="O184" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -22246,7 +22302,7 @@
         <v>76</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>74</v>
@@ -23000,7 +23056,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>311</v>
@@ -23103,13 +23159,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -23206,13 +23262,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -23220,7 +23276,7 @@
       </c>
       <c r="F194" s="2"/>
       <c r="G194" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>75</v>
@@ -23309,16 +23365,16 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B195" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="D195" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="D195" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="E195" t="s" s="2">
         <v>76</v>
@@ -23343,7 +23399,7 @@
         <v>126</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N195" t="s" s="2">
         <v>312</v>
@@ -23414,13 +23470,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B196" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C196" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -23517,13 +23573,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B197" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -23620,13 +23676,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B198" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C198" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="C198" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -23652,13 +23708,13 @@
         <v>96</v>
       </c>
       <c r="M198" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N198" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="N198" t="s" s="2">
+      <c r="O198" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="O198" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="P198" s="2"/>
       <c r="Q198" t="s" s="2">
@@ -23666,7 +23722,7 @@
       </c>
       <c r="R198" s="2"/>
       <c r="S198" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="T198" t="s" s="2">
         <v>76</v>
@@ -23708,7 +23764,7 @@
         <v>76</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>82</v>
@@ -23725,13 +23781,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B199" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C199" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="C199" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -23757,10 +23813,10 @@
         <v>188</v>
       </c>
       <c r="M199" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N199" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" s="2"/>
@@ -23791,25 +23847,25 @@
       </c>
       <c r="Z199" s="2"/>
       <c r="AA199" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AB199" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC199" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD199" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE199" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF199" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG199" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="AB199" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC199" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD199" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE199" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF199" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG199" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>74</v>
@@ -23826,23 +23882,23 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B200" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="D200" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="D200" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="E200" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F200" s="2"/>
       <c r="G200" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>82</v>
@@ -23860,7 +23916,7 @@
         <v>126</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="N200" t="s" s="2">
         <v>312</v>
@@ -23931,13 +23987,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -24034,13 +24090,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -24137,13 +24193,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -24169,13 +24225,13 @@
         <v>96</v>
       </c>
       <c r="M203" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N203" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="N203" t="s" s="2">
+      <c r="O203" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="P203" s="2"/>
       <c r="Q203" t="s" s="2">
@@ -24183,7 +24239,7 @@
       </c>
       <c r="R203" s="2"/>
       <c r="S203" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="T203" t="s" s="2">
         <v>76</v>
@@ -24225,7 +24281,7 @@
         <v>76</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>82</v>
@@ -24242,13 +24298,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -24274,10 +24330,10 @@
         <v>255</v>
       </c>
       <c r="M204" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N204" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
@@ -24328,7 +24384,7 @@
         <v>76</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>74</v>
@@ -24345,13 +24401,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>689</v>
+        <v>703</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -24359,7 +24415,7 @@
       </c>
       <c r="F205" s="2"/>
       <c r="G205" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>82</v>
@@ -24374,24 +24430,22 @@
         <v>76</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>96</v>
+        <v>215</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>686</v>
+        <v>216</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>688</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="O205" s="2"/>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
         <v>76</v>
       </c>
       <c r="R205" s="2"/>
       <c r="S205" t="s" s="2">
-        <v>669</v>
+        <v>76</v>
       </c>
       <c r="T205" t="s" s="2">
         <v>76</v>
@@ -24433,10 +24487,10 @@
         <v>76</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>689</v>
+        <v>218</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>82</v>
@@ -24450,24 +24504,24 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="F206" s="2"/>
       <c r="G206" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>76</v>
@@ -24479,15 +24533,17 @@
         <v>76</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>703</v>
+        <v>126</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>692</v>
+        <v>127</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="O206" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O206" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
         <v>76</v>
@@ -24524,30 +24580,450 @@
         <v>76</v>
       </c>
       <c r="AC206" t="s" s="2">
-        <v>76</v>
+        <v>313</v>
       </c>
       <c r="AD206" t="s" s="2">
-        <v>76</v>
+        <v>323</v>
       </c>
       <c r="AE206" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>695</v>
+        <v>221</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AJ206" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AK206" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C207" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="D207" s="2"/>
+      <c r="E207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F207" s="2"/>
+      <c r="G207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K207" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L207" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M207" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O207" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="P207" s="2"/>
+      <c r="Q207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R207" s="2"/>
+      <c r="S207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF207" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG207" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AH207" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI207" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ207" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AK207" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="C208" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="D208" s="2"/>
+      <c r="E208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F208" s="2"/>
+      <c r="G208" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H208" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K208" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L208" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M208" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="P208" s="2"/>
+      <c r="Q208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R208" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="S208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF208" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG208" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AH208" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI208" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ208" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AK208" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C209" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="D209" s="2"/>
+      <c r="E209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F209" s="2"/>
+      <c r="G209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="L209" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M209" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="P209" s="2"/>
+      <c r="Q209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R209" s="2"/>
+      <c r="S209" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="T209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG209" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AH209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI209" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ209" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK209" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="D210" s="2"/>
+      <c r="E210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F210" s="2"/>
+      <c r="G210" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H210" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="L210" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M210" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O210" s="2"/>
+      <c r="P210" s="2"/>
+      <c r="Q210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R210" s="2"/>
+      <c r="S210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG210" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AH210" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI210" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ210" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK210" t="s" s="2">
         <v>94</v>
       </c>
     </row>
